--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ARKANSAS_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ARKANSAS_2014.xlsx
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C213">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C223">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C527">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C581">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C598">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C928">
